--- a/public/system/export/borrowdevicesuser.xlsx
+++ b/public/system/export/borrowdevicesuser.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>STT</t>
   </si>
@@ -61,24 +61,12 @@
     <t>Số</t>
   </si>
   <si>
-    <t>Bộ thí nghiệm mô men quán tính của vật rắn (1)</t>
-  </si>
-  <si>
     <t>SL</t>
   </si>
   <si>
     <t>Lớp</t>
   </si>
   <si>
-    <t>thực hành tông hợp lực</t>
-  </si>
-  <si>
-    <t>12C3</t>
-  </si>
-  <si>
-    <t>Ổn</t>
-  </si>
-  <si>
     <t>Giáo Viên</t>
   </si>
   <si>
@@ -86,12 +74,6 @@
   </si>
   <si>
     <t>Ngày tạo</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thu Thủy</t>
-  </si>
-  <si>
-    <t>23/10/2024</t>
   </si>
   <si>
     <t>Giáo viên:</t>
@@ -275,16 +257,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -294,14 +282,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,40 +512,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15" customHeight="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
     </row>
     <row r="2" spans="1:13" ht="15" customHeight="1">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
     </row>
     <row r="3" spans="1:13" ht="15" customHeight="1">
       <c r="A3" s="1"/>
@@ -575,20 +557,20 @@
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:13" ht="25.5" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22"/>
-      <c r="K4" s="22"/>
-      <c r="L4" s="22"/>
+      <c r="A4" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
     </row>
     <row r="5" spans="1:13" ht="15" customHeight="1">
       <c r="A5" s="1"/>
@@ -605,115 +587,95 @@
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="6" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F6" s="9"/>
-      <c r="G6" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="18"/>
+      <c r="G6" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="22"/>
       <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:13" ht="15" customHeight="1">
       <c r="E7" s="6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="18"/>
+      <c r="H7" s="22"/>
       <c r="I7" s="8"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="20"/>
+      <c r="E9" s="18"/>
       <c r="F9" s="19" t="s">
         <v>10</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H9" s="19" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="I9" s="19" t="s">
         <v>11</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K9" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="L9" s="21" t="s">
-        <v>19</v>
+      <c r="L9" s="23" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="30" customHeight="1">
-      <c r="A10" s="20"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="20"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+        <v>17</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="1:13" ht="15.75" customHeight="1">
       <c r="A11" s="10">
         <v>1</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="11">
-        <v>1</v>
-      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>22</v>
-      </c>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="14"/>
     </row>
     <row r="12" spans="1:13" ht="15.75" customHeight="1">
       <c r="A12" s="15">
@@ -1849,6 +1811,8 @@
     <row r="1008" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="A2:D2"/>
@@ -1865,8 +1829,6 @@
     <mergeCell ref="J9:J10"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
   </mergeCells>
   <pageMargins left="0.51" right="0.54" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
